--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC3FA63-71BF-4721-94E7-E56BF7B244B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35A23E2-00DA-4F9A-955E-D25E52CAB5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Course Navette</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Atleta</t>
+  </si>
+  <si>
+    <t>Fecha</t>
   </si>
 </sst>
 </file>
@@ -218,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -226,6 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -528,21 +532,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -550,48 +555,51 @@
         <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
+      <c r="C2" s="3">
+        <v>45958</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -623,16 +631,19 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
+      <c r="C3" s="3">
+        <v>45958</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -664,16 +675,19 @@
       <c r="M3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
+      <c r="C4" s="3">
+        <v>45958</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -705,16 +719,19 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
+      <c r="C5" s="3">
+        <v>45958</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -746,16 +763,19 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
+      <c r="C6" s="3">
+        <v>45958</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -787,16 +807,19 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
+      <c r="C7" s="3">
+        <v>45958</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -828,16 +851,19 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
+      <c r="C8" s="3">
+        <v>45958</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -869,16 +895,19 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
+      <c r="C9" s="3">
+        <v>45958</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -910,16 +939,19 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
+      <c r="C10" s="3">
+        <v>45958</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -951,16 +983,19 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
+      <c r="C11" s="3">
+        <v>45958</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -992,16 +1027,19 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
+      <c r="C12" s="3">
+        <v>45958</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1033,16 +1071,19 @@
       <c r="M12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
+      <c r="C13" s="3">
+        <v>45958</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -1074,16 +1115,19 @@
       <c r="M13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
+      <c r="C14" s="3">
+        <v>45958</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
@@ -1115,16 +1159,19 @@
       <c r="M14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
       <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2">
-        <v>0</v>
+      <c r="C15" s="3">
+        <v>45958</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
@@ -1154,6 +1201,9 @@
         <v>0</v>
       </c>
       <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
         <v>0</v>
       </c>
     </row>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35A23E2-00DA-4F9A-955E-D25E52CAB5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CDECCA-DDD3-4BBC-A49D-A11A8C786444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,39 +35,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
-    <t>Course Navette</t>
-  </si>
-  <si>
-    <t>Dinamometria Der.</t>
-  </si>
-  <si>
-    <t>Dinamometria Izq.</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>100 m</t>
-  </si>
-  <si>
-    <t>500 m</t>
-  </si>
-  <si>
-    <t>5 km</t>
-  </si>
-  <si>
-    <t>10 km</t>
-  </si>
-  <si>
     <t>12 x400 m</t>
   </si>
   <si>
-    <t>CMJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salto largo </t>
-  </si>
-  <si>
     <t>D2/D4</t>
   </si>
   <si>
@@ -159,6 +132,33 @@
   </si>
   <si>
     <t>Fecha</t>
+  </si>
+  <si>
+    <t>100m (s)</t>
+  </si>
+  <si>
+    <t>400m (s)</t>
+  </si>
+  <si>
+    <t>5k (min)</t>
+  </si>
+  <si>
+    <t>10km (min)</t>
+  </si>
+  <si>
+    <t>Course Navette (max)</t>
+  </si>
+  <si>
+    <t>Salto Largo (cm)</t>
+  </si>
+  <si>
+    <t>Salto Alto (cm)</t>
+  </si>
+  <si>
+    <t>Dinamometria Izq (kg)</t>
+  </si>
+  <si>
+    <t>Dinamometria Der (kg)</t>
   </si>
 </sst>
 </file>
@@ -538,65 +538,67 @@
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.5703125" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3">
         <v>45958</v>
@@ -637,10 +639,10 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3">
         <v>45958</v>
@@ -681,10 +683,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3">
         <v>45958</v>
@@ -725,10 +727,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <v>45958</v>
@@ -769,10 +771,10 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3">
         <v>45958</v>
@@ -813,10 +815,10 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3">
         <v>45958</v>
@@ -857,10 +859,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3">
         <v>45958</v>
@@ -901,10 +903,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>45958</v>
@@ -945,10 +947,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3">
         <v>45958</v>
@@ -989,10 +991,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
         <v>45958</v>
@@ -1033,10 +1035,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3">
         <v>45958</v>
@@ -1077,10 +1079,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3">
         <v>45958</v>
@@ -1121,10 +1123,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C14" s="3">
         <v>45958</v>
@@ -1165,10 +1167,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3">
         <v>45958</v>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CDECCA-DDD3-4BBC-A49D-A11A8C786444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD9DC55-B74B-44B1-B224-79BE8E389926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -603,39 +603,17 @@
       <c r="C2" s="3">
         <v>45958</v>
       </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -647,39 +625,17 @@
       <c r="C3" s="3">
         <v>45958</v>
       </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -691,39 +647,17 @@
       <c r="C4" s="3">
         <v>45958</v>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -735,39 +669,17 @@
       <c r="C5" s="3">
         <v>45958</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -779,39 +691,17 @@
       <c r="C6" s="3">
         <v>45958</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>0</v>
-      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -823,39 +713,17 @@
       <c r="C7" s="3">
         <v>45958</v>
       </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -867,39 +735,17 @@
       <c r="C8" s="3">
         <v>45958</v>
       </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -911,39 +757,17 @@
       <c r="C9" s="3">
         <v>45958</v>
       </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -955,39 +779,17 @@
       <c r="C10" s="3">
         <v>45958</v>
       </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -999,39 +801,17 @@
       <c r="C11" s="3">
         <v>45958</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2">
-        <v>0</v>
-      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1043,39 +823,17 @@
       <c r="C12" s="3">
         <v>45958</v>
       </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2">
-        <v>0</v>
-      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1087,39 +845,17 @@
       <c r="C13" s="3">
         <v>45958</v>
       </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2">
-        <v>0</v>
-      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1131,39 +867,17 @@
       <c r="C14" s="3">
         <v>45958</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2">
-        <v>0</v>
-      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1175,39 +889,17 @@
       <c r="C15" s="3">
         <v>45958</v>
       </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2">
-        <v>0</v>
-      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD9DC55-B74B-44B1-B224-79BE8E389926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47ACDCC-8E43-441F-B2C7-33F442E0133D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -532,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -625,7 +625,9 @@
       <c r="C3" s="3">
         <v>45958</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>50</v>
+      </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -901,6 +903,76 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
     </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3">
+        <v>45958</v>
+      </c>
+      <c r="D16" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>45958</v>
+      </c>
+      <c r="D17" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3">
+        <v>45958</v>
+      </c>
+      <c r="D18" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>45958</v>
+      </c>
+      <c r="D19" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3">
+        <v>45958</v>
+      </c>
+      <c r="D20" s="2">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47ACDCC-8E43-441F-B2C7-33F442E0133D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023A30F9-C4AB-4E99-AFB6-9FF0C8CA22FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -625,9 +625,7 @@
       <c r="C3" s="3">
         <v>45958</v>
       </c>
-      <c r="D3" s="2">
-        <v>50</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -904,74 +902,24 @@
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3">
-        <v>45958</v>
-      </c>
-      <c r="D16" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="3">
-        <v>45958</v>
-      </c>
-      <c r="D17" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="3">
-        <v>45958</v>
-      </c>
-      <c r="D18" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="3">
-        <v>45958</v>
-      </c>
-      <c r="D19" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="3">
-        <v>45958</v>
-      </c>
-      <c r="D20" s="2">
-        <v>35</v>
-      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="3"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="3"/>
+      <c r="D20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023A30F9-C4AB-4E99-AFB6-9FF0C8CA22FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077FF74B-3B8D-4CFA-813F-20D3DFBF9125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>Dinamometria Der (kg)</t>
+  </si>
+  <si>
+    <t>0.947 → Alto nivel de testosterona</t>
   </si>
 </sst>
 </file>
@@ -532,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -545,7 +548,7 @@
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" customWidth="1"/>
+    <col min="14" max="14" width="32" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -584,10 +587,10 @@
         <v>38</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
@@ -635,7 +638,9 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -902,24 +907,264 @@
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="3"/>
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3">
+        <v>45889.481031226853</v>
+      </c>
       <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="3"/>
+      <c r="L16">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="M16">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>45443</v>
+      </c>
       <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="3"/>
+      <c r="L17">
+        <v>38.5</v>
+      </c>
+      <c r="M17">
+        <v>32.700000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3">
+        <v>45473</v>
+      </c>
       <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="3"/>
+      <c r="L18">
+        <v>41.8</v>
+      </c>
+      <c r="M18">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>45504</v>
+      </c>
       <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="3"/>
+      <c r="L19">
+        <v>41.3</v>
+      </c>
+      <c r="M19">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3">
+        <v>45535</v>
+      </c>
       <c r="D20" s="2"/>
+      <c r="L20">
+        <v>41.4</v>
+      </c>
+      <c r="M20">
+        <v>37.700000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>45565</v>
+      </c>
+      <c r="L21">
+        <v>44.5</v>
+      </c>
+      <c r="M21">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="3">
+        <v>45596</v>
+      </c>
+      <c r="L22">
+        <v>44.8</v>
+      </c>
+      <c r="M22">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3">
+        <v>45626</v>
+      </c>
+      <c r="L23">
+        <v>45.6</v>
+      </c>
+      <c r="M23">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="3">
+        <v>45655</v>
+      </c>
+      <c r="L24">
+        <v>46.1</v>
+      </c>
+      <c r="M24">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3">
+        <v>45688</v>
+      </c>
+      <c r="L25">
+        <v>43.9</v>
+      </c>
+      <c r="M25">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3">
+        <v>45746</v>
+      </c>
+      <c r="L26">
+        <v>42.9</v>
+      </c>
+      <c r="M26">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3">
+        <v>45777</v>
+      </c>
+      <c r="L27">
+        <v>42.9</v>
+      </c>
+      <c r="M27">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="3">
+        <v>45808</v>
+      </c>
+      <c r="L28">
+        <v>52.8</v>
+      </c>
+      <c r="M28">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="3">
+        <v>45838</v>
+      </c>
+      <c r="L29">
+        <v>48.7</v>
+      </c>
+      <c r="M29">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="3">
+        <v>45869</v>
+      </c>
+      <c r="L30">
+        <v>44.4</v>
+      </c>
+      <c r="M30">
+        <v>42.1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077FF74B-3B8D-4CFA-813F-20D3DFBF9125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E0F027-94ED-48D7-A212-7E667934FD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -161,7 +161,10 @@
     <t>Dinamometria Der (kg)</t>
   </si>
   <si>
-    <t>0.947 → Alto nivel de testosterona</t>
+    <t xml:space="preserve">0.947 </t>
+  </si>
+  <si>
+    <t>Illinois</t>
   </si>
 </sst>
 </file>
@@ -535,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -548,11 +551,11 @@
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,8 +598,11 @@
       <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -618,7 +624,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -642,7 +648,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -664,7 +670,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -686,7 +692,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -708,7 +714,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -730,7 +736,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -752,7 +758,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -774,7 +780,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -796,7 +802,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -818,7 +824,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -840,7 +846,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -862,7 +868,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -884,7 +890,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -906,7 +912,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E0F027-94ED-48D7-A212-7E667934FD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEA9489-CBD0-49DC-AD63-2026FB42320B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,12 +149,6 @@
     <t>Course Navette (max)</t>
   </si>
   <si>
-    <t>Salto Largo (cm)</t>
-  </si>
-  <si>
-    <t>Salto Alto (cm)</t>
-  </si>
-  <si>
     <t>Dinamometria Izq (kg)</t>
   </si>
   <si>
@@ -164,7 +158,13 @@
     <t xml:space="preserve">0.947 </t>
   </si>
   <si>
-    <t>Illinois</t>
+    <t>5x10</t>
+  </si>
+  <si>
+    <t>Salto Largo (m)</t>
+  </si>
+  <si>
+    <t>Test Bosco (cm)</t>
   </si>
 </sst>
 </file>
@@ -584,22 +584,22 @@
         <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -640,12 +640,19 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="J3" s="2">
+        <v>58.3</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2.79</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="O3">
+        <v>32.47</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -664,11 +671,18 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="J4" s="2">
+        <v>46.33</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
+      <c r="O4">
+        <v>35.979999999999997</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -686,11 +700,18 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2.0299999999999998</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
+      <c r="O5">
+        <v>34.28</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -708,11 +729,18 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2.09</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
+      <c r="O6">
+        <v>34.869999999999997</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -730,11 +758,18 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2">
+        <v>42.8</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2.1800000000000002</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
+      <c r="O7">
+        <v>32.71</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -752,11 +787,18 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="J8" s="2">
+        <v>43</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2.2200000000000002</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
+      <c r="O8">
+        <v>34.67</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -774,11 +816,18 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="J9" s="2">
+        <v>38.54</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2.44</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
+      <c r="O9">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -796,11 +845,18 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="J10" s="2">
+        <v>41</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1.92</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
+      <c r="O10">
+        <v>35.65</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -818,11 +874,18 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
+      <c r="O11">
+        <v>43.19</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -840,11 +903,18 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="J12" s="2">
+        <v>32</v>
+      </c>
+      <c r="K12" s="2">
+        <v>2.08</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
+      <c r="O12">
+        <v>35.17</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -862,11 +932,18 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="J13" s="2">
+        <v>31</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1.99</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
+      <c r="O13">
+        <v>36.71</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -884,11 +961,18 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
+      <c r="O14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -906,11 +990,18 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="J15" s="2">
+        <v>45</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2.15</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
+      <c r="O15">
+        <v>35.29</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEA9489-CBD0-49DC-AD63-2026FB42320B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43749449-03CD-49A5-837C-1F834A398C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
   <si>
     <t>ID</t>
   </si>
@@ -165,13 +165,28 @@
   </si>
   <si>
     <t>Test Bosco (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1Zm1tbAyfsYkMkPUZStJ5m8mbyLZkrGOo?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/drive/folders/1q6TxeOAlrtPNfrKsxW_zUw9HX_scEaHp?usp=drive_link </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/drive/folders/1CtcI-qsRkmNACGf7v_iqOMK_OOt9pTlU?usp=drive_link </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="5" formatCode="&quot;XDR&quot;#,##0;\-&quot;XDR&quot;#,##0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +202,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -224,10 +247,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -236,8 +260,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -538,12 +565,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -553,9 +580,10 @@
     <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.5703125" customWidth="1"/>
+    <col min="16" max="16" width="86.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,9 +629,12 @@
       <c r="O1" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -624,8 +655,8 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
@@ -654,9 +685,12 @@
       <c r="O3">
         <v>32.47</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="P3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
@@ -684,8 +718,8 @@
         <v>35.979999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
@@ -713,8 +747,8 @@
         <v>34.28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
@@ -741,9 +775,12 @@
       <c r="O6">
         <v>34.869999999999997</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="P6" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
@@ -771,8 +808,8 @@
         <v>32.71</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B8" t="s">
@@ -800,8 +837,8 @@
         <v>34.67</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
@@ -829,8 +866,8 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
@@ -858,8 +895,8 @@
         <v>35.65</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
@@ -887,8 +924,8 @@
         <v>43.19</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B12" t="s">
@@ -916,8 +953,8 @@
         <v>35.17</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
@@ -944,9 +981,12 @@
       <c r="O13">
         <v>36.71</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="P13" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B14" t="s">
@@ -974,8 +1014,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B15" t="s">
@@ -1003,8 +1043,8 @@
         <v>35.29</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B16" t="s">
@@ -1022,7 +1062,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B17" t="s">
@@ -1040,7 +1080,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B18" t="s">
@@ -1058,7 +1098,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B19" t="s">
@@ -1076,7 +1116,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B20" t="s">
@@ -1094,7 +1134,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B21" t="s">
@@ -1111,7 +1151,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B22" t="s">
@@ -1128,7 +1168,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B23" t="s">
@@ -1145,7 +1185,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B24" t="s">
@@ -1162,7 +1202,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B25" t="s">
@@ -1179,7 +1219,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B26" t="s">
@@ -1196,7 +1236,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B27" t="s">
@@ -1213,7 +1253,7 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B28" t="s">
@@ -1230,7 +1270,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B29" t="s">
@@ -1247,7 +1287,7 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B30" t="s">
@@ -1265,6 +1305,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="P3" r:id="rId1" xr:uid="{D37F6C56-8B7C-4D45-927E-348BD9AC56A7}"/>
+    <hyperlink ref="P6" r:id="rId2" xr:uid="{4F4065F7-F4C1-499C-A916-4B5D051ECD9D}"/>
+    <hyperlink ref="P13" r:id="rId3" xr:uid="{59F0DF20-A2AC-4E32-B952-1820DEF5D9D5}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43749449-03CD-49A5-837C-1F834A398C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744E1C0F-0ECE-4F2D-8C46-5938C3D1BA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
